--- a/public/templates/QS_聯絡人匯入樣板.xlsx
+++ b/public/templates/QS_聯絡人匯入樣板.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="679">
   <si>
     <t>QS 聯絡人匯入樣板 — 填寫說明</t>
   </si>
@@ -48,13 +48,16 @@
     <t>• 其他分頁為選項對照表（下拉選單來源），亦可手動查閱。</t>
   </si>
   <si>
+    <t>• 黃色欄位為「Other 說明」：下拉選單選 Other 後，在旁邊黃色欄自行填寫（不必改下拉選單那一格）。</t>
+  </si>
+  <si>
     <t>三、共通規則</t>
   </si>
   <si>
     <t>• Source 請選 Fo Guang University。</t>
   </si>
   <si>
-    <t>• Title／職稱／產業／學科／國家等請用下拉選單；若選 Other，請改為 Others (說明) 或 Other (說明) 格式。</t>
+    <t>• Title／職稱／產業／學科／國家等用下拉選單；選 Other 時在右邊黃色欄填寫。</t>
   </si>
   <si>
     <t>• 姓名、系所、機構、Email、電話請手動輸入。</t>
@@ -1974,6 +1977,10 @@
     <t>Title</t>
   </si>
   <si>
+    <t xml:space="preserve">Title Other
+（選 Other 時填）</t>
+  </si>
+  <si>
     <t>First Name</t>
   </si>
   <si>
@@ -1983,6 +1990,10 @@
     <t>Job Title</t>
   </si>
   <si>
+    <t xml:space="preserve">Job Title Other
+（選 Other 時填）</t>
+  </si>
+  <si>
     <t>Department</t>
   </si>
   <si>
@@ -1992,12 +2003,20 @@
     <t>Country or Territory</t>
   </si>
   <si>
+    <t xml:space="preserve">Country Other
+（選 Other 時填）</t>
+  </si>
+  <si>
     <t>Email</t>
   </si>
   <si>
     <t>Subject</t>
   </si>
   <si>
+    <t xml:space="preserve">Subject Other
+（選 Other 時填）</t>
+  </si>
+  <si>
     <t>Phone (Optional)</t>
   </si>
   <si>
@@ -2022,7 +2041,15 @@
     <t>Position</t>
   </si>
   <si>
+    <t xml:space="preserve">Position Other
+（選 Other 時填）</t>
+  </si>
+  <si>
     <t>Industry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Industry Other
+（選 Other 時填）</t>
   </si>
   <si>
     <t>Company Name</t>
@@ -2078,7 +2105,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2088,6 +2115,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1D4ED8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE68A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFBEB"/>
       </patternFill>
     </fill>
   </fills>
@@ -2118,7 +2155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2128,9 +2165,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2473,7 +2517,7 @@
   <sheetPr>
     <tabColor rgb="FF64748B"/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="95" customWidth="1"/>
@@ -2531,12 +2575,12 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -2566,12 +2610,12 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
@@ -2581,12 +2625,17 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>17</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -2608,90 +2657,90 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -2715,130 +2764,130 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -2862,98 +2911,98 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -2977,234 +3026,234 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -3222,496 +3271,496 @@
   <dimension ref="A1:B61"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -3735,1586 +3784,1586 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="184" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="185" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="186" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="187" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="188" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="189" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="190" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="191" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="194" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="195" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="196" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="197" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="198" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -5329,191 +5378,715 @@
   <sheetPr>
     <tabColor rgb="FFDC2626"/>
   </sheetPr>
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:O101"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="31" customWidth="1"/>
-    <col min="6" max="6" width="23" customWidth="1"/>
-    <col min="7" max="7" width="21" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="31" customWidth="1"/>
+    <col min="7" max="7" width="25" customWidth="1"/>
+    <col min="8" max="8" width="23" customWidth="1"/>
+    <col min="9" max="9" width="21" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="11" width="23" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="23" customWidth="1"/>
+    <col min="15" max="15" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="C1" s="3" t="s">
         <v>651</v>
       </c>
+      <c r="C1" s="5" t="s">
+        <v>652</v>
+      </c>
       <c r="D1" s="3" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>654</v>
-      </c>
-      <c r="G1" s="3" t="s">
         <v>655</v>
       </c>
+      <c r="G1" s="5" t="s">
+        <v>656</v>
+      </c>
       <c r="H1" s="3" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>658</v>
-      </c>
-      <c r="K1" s="3" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="2" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>660</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="L1" s="3" t="s">
         <v>661</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="M1" s="3" t="s">
         <v>662</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F2" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>663</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>660</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>601</v>
-      </c>
-      <c r="I2" s="5" t="s">
+      <c r="O1" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="K2" s="5" t="s">
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>665</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25"/>
+      <c r="B2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>666</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>667</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>668</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>665</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>669</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="N3" s="8"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="N4" s="8"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="N5" s="8"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="N6" s="8"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="N7" s="8"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="N8" s="8"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="N9" s="8"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="N10" s="8"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="N11" s="8"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="N12" s="8"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="N13" s="8"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="N14" s="8"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="N15" s="8"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="N16" s="8"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="N17" s="8"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="N18" s="8"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="N19" s="8"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="N20" s="8"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="N21" s="8"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="N22" s="8"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="N23" s="8"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="N24" s="8"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="N25" s="8"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="N26" s="8"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="N27" s="8"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="N28" s="8"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="N29" s="8"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="N30" s="8"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="N31" s="8"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="N32" s="8"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="N33" s="8"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="N34" s="8"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="N35" s="8"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="N36" s="8"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="N37" s="8"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="K38" s="8"/>
+      <c r="N38" s="8"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="N39" s="8"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="K40" s="8"/>
+      <c r="N40" s="8"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="K41" s="8"/>
+      <c r="N41" s="8"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C42" s="8"/>
+      <c r="G42" s="8"/>
+      <c r="K42" s="8"/>
+      <c r="N42" s="8"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C43" s="8"/>
+      <c r="G43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="N43" s="8"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="N44" s="8"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C45" s="8"/>
+      <c r="G45" s="8"/>
+      <c r="K45" s="8"/>
+      <c r="N45" s="8"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C46" s="8"/>
+      <c r="G46" s="8"/>
+      <c r="K46" s="8"/>
+      <c r="N46" s="8"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="N47" s="8"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C48" s="8"/>
+      <c r="G48" s="8"/>
+      <c r="K48" s="8"/>
+      <c r="N48" s="8"/>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C49" s="8"/>
+      <c r="G49" s="8"/>
+      <c r="K49" s="8"/>
+      <c r="N49" s="8"/>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C50" s="8"/>
+      <c r="G50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="N50" s="8"/>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="N51" s="8"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="N52" s="8"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="N53" s="8"/>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C54" s="8"/>
+      <c r="G54" s="8"/>
+      <c r="K54" s="8"/>
+      <c r="N54" s="8"/>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C55" s="8"/>
+      <c r="G55" s="8"/>
+      <c r="K55" s="8"/>
+      <c r="N55" s="8"/>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C56" s="8"/>
+      <c r="G56" s="8"/>
+      <c r="K56" s="8"/>
+      <c r="N56" s="8"/>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C57" s="8"/>
+      <c r="G57" s="8"/>
+      <c r="K57" s="8"/>
+      <c r="N57" s="8"/>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C58" s="8"/>
+      <c r="G58" s="8"/>
+      <c r="K58" s="8"/>
+      <c r="N58" s="8"/>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C59" s="8"/>
+      <c r="G59" s="8"/>
+      <c r="K59" s="8"/>
+      <c r="N59" s="8"/>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C60" s="8"/>
+      <c r="G60" s="8"/>
+      <c r="K60" s="8"/>
+      <c r="N60" s="8"/>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C61" s="8"/>
+      <c r="G61" s="8"/>
+      <c r="K61" s="8"/>
+      <c r="N61" s="8"/>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C62" s="8"/>
+      <c r="G62" s="8"/>
+      <c r="K62" s="8"/>
+      <c r="N62" s="8"/>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C63" s="8"/>
+      <c r="G63" s="8"/>
+      <c r="K63" s="8"/>
+      <c r="N63" s="8"/>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C64" s="8"/>
+      <c r="G64" s="8"/>
+      <c r="K64" s="8"/>
+      <c r="N64" s="8"/>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C65" s="8"/>
+      <c r="G65" s="8"/>
+      <c r="K65" s="8"/>
+      <c r="N65" s="8"/>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C66" s="8"/>
+      <c r="G66" s="8"/>
+      <c r="K66" s="8"/>
+      <c r="N66" s="8"/>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C67" s="8"/>
+      <c r="G67" s="8"/>
+      <c r="K67" s="8"/>
+      <c r="N67" s="8"/>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C68" s="8"/>
+      <c r="G68" s="8"/>
+      <c r="K68" s="8"/>
+      <c r="N68" s="8"/>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C69" s="8"/>
+      <c r="G69" s="8"/>
+      <c r="K69" s="8"/>
+      <c r="N69" s="8"/>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C70" s="8"/>
+      <c r="G70" s="8"/>
+      <c r="K70" s="8"/>
+      <c r="N70" s="8"/>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C71" s="8"/>
+      <c r="G71" s="8"/>
+      <c r="K71" s="8"/>
+      <c r="N71" s="8"/>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C72" s="8"/>
+      <c r="G72" s="8"/>
+      <c r="K72" s="8"/>
+      <c r="N72" s="8"/>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C73" s="8"/>
+      <c r="G73" s="8"/>
+      <c r="K73" s="8"/>
+      <c r="N73" s="8"/>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C74" s="8"/>
+      <c r="G74" s="8"/>
+      <c r="K74" s="8"/>
+      <c r="N74" s="8"/>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C75" s="8"/>
+      <c r="G75" s="8"/>
+      <c r="K75" s="8"/>
+      <c r="N75" s="8"/>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C76" s="8"/>
+      <c r="G76" s="8"/>
+      <c r="K76" s="8"/>
+      <c r="N76" s="8"/>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C77" s="8"/>
+      <c r="G77" s="8"/>
+      <c r="K77" s="8"/>
+      <c r="N77" s="8"/>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C78" s="8"/>
+      <c r="G78" s="8"/>
+      <c r="K78" s="8"/>
+      <c r="N78" s="8"/>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C79" s="8"/>
+      <c r="G79" s="8"/>
+      <c r="K79" s="8"/>
+      <c r="N79" s="8"/>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C80" s="8"/>
+      <c r="G80" s="8"/>
+      <c r="K80" s="8"/>
+      <c r="N80" s="8"/>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C81" s="8"/>
+      <c r="G81" s="8"/>
+      <c r="K81" s="8"/>
+      <c r="N81" s="8"/>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C82" s="8"/>
+      <c r="G82" s="8"/>
+      <c r="K82" s="8"/>
+      <c r="N82" s="8"/>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C83" s="8"/>
+      <c r="G83" s="8"/>
+      <c r="K83" s="8"/>
+      <c r="N83" s="8"/>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C84" s="8"/>
+      <c r="G84" s="8"/>
+      <c r="K84" s="8"/>
+      <c r="N84" s="8"/>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C85" s="8"/>
+      <c r="G85" s="8"/>
+      <c r="K85" s="8"/>
+      <c r="N85" s="8"/>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C86" s="8"/>
+      <c r="G86" s="8"/>
+      <c r="K86" s="8"/>
+      <c r="N86" s="8"/>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C87" s="8"/>
+      <c r="G87" s="8"/>
+      <c r="K87" s="8"/>
+      <c r="N87" s="8"/>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C88" s="8"/>
+      <c r="G88" s="8"/>
+      <c r="K88" s="8"/>
+      <c r="N88" s="8"/>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C89" s="8"/>
+      <c r="G89" s="8"/>
+      <c r="K89" s="8"/>
+      <c r="N89" s="8"/>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C90" s="8"/>
+      <c r="G90" s="8"/>
+      <c r="K90" s="8"/>
+      <c r="N90" s="8"/>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C91" s="8"/>
+      <c r="G91" s="8"/>
+      <c r="K91" s="8"/>
+      <c r="N91" s="8"/>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C92" s="8"/>
+      <c r="G92" s="8"/>
+      <c r="K92" s="8"/>
+      <c r="N92" s="8"/>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C93" s="8"/>
+      <c r="G93" s="8"/>
+      <c r="K93" s="8"/>
+      <c r="N93" s="8"/>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C94" s="8"/>
+      <c r="G94" s="8"/>
+      <c r="K94" s="8"/>
+      <c r="N94" s="8"/>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C95" s="8"/>
+      <c r="G95" s="8"/>
+      <c r="K95" s="8"/>
+      <c r="N95" s="8"/>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C96" s="8"/>
+      <c r="G96" s="8"/>
+      <c r="K96" s="8"/>
+      <c r="N96" s="8"/>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C97" s="8"/>
+      <c r="G97" s="8"/>
+      <c r="K97" s="8"/>
+      <c r="N97" s="8"/>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C98" s="8"/>
+      <c r="G98" s="8"/>
+      <c r="K98" s="8"/>
+      <c r="N98" s="8"/>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C99" s="8"/>
+      <c r="G99" s="8"/>
+      <c r="K99" s="8"/>
+      <c r="N99" s="8"/>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C100" s="8"/>
+      <c r="G100" s="8"/>
+      <c r="K100" s="8"/>
+      <c r="N100" s="8"/>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C101" s="8"/>
+      <c r="G101" s="8"/>
+      <c r="K101" s="8"/>
+      <c r="N101" s="8"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:O2"/>
   <dataValidations count="10">
     <dataValidation type="list" showInputMessage="1" promptTitle="Source" prompt="請選擇 Fo Guang University" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="A10:A101">
       <formula1>"Fo Guang University"</formula1>
@@ -5521,28 +6094,28 @@
     <dataValidation type="list" showInputMessage="1" promptTitle="Source" prompt="請選擇 Fo Guang University" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="A2:A101">
       <formula1>"Fo Guang University"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Title" prompt="請選擇稱謂" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="B10:B101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Title" prompt="請選擇稱謂；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="B10:B101">
       <formula1>'稱謂'!$A$2:$A$11</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Title" prompt="請選擇稱謂" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="B2:B101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Title" prompt="請選擇稱謂；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="B2:B101">
       <formula1>'稱謂'!$A$2:$A$11</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Job Title" prompt="請選擇學術職稱" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="E10:E101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Job Title" prompt="請選擇學術職稱；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="F10:F101">
       <formula1>'學術職稱'!$A$2:$A$16</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Job Title" prompt="請選擇學術職稱" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="E2:E101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Job Title" prompt="請選擇學術職稱；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="F2:F101">
       <formula1>'學術職稱'!$A$2:$A$16</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Country" prompt="請選擇國家或地區" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="H10:H101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Country" prompt="請選擇國家或地區；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="J10:J101">
       <formula1>'國家或地區'!$A$2:$A$198</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Country" prompt="請選擇國家或地區" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="H2:H101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Country" prompt="請選擇國家或地區；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="J2:J101">
       <formula1>'國家或地區'!$A$2:$A$198</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Subject" prompt="請選擇學科領域" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="J10:J101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Subject" prompt="請選擇學科領域；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="M10:M101">
       <formula1>'學科領域'!$A$2:$A$61</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Subject" prompt="請選擇學科領域" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="J2:J101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Subject" prompt="請選擇學科領域；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="M2:M101">
       <formula1>'學科領域'!$A$2:$A$61</formula1>
     </dataValidation>
   </dataValidations>
@@ -5556,183 +6129,707 @@
   <sheetPr>
     <tabColor rgb="FFF59E0B"/>
   </sheetPr>
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:N101"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="10" max="11" width="22" customWidth="1"/>
+    <col min="12" max="12" width="23" customWidth="1"/>
+    <col min="13" max="13" width="15" customWidth="1"/>
+    <col min="14" max="14" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="C1" s="3" t="s">
         <v>651</v>
       </c>
+      <c r="C1" s="5" t="s">
+        <v>652</v>
+      </c>
       <c r="D1" s="3" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>668</v>
+        <v>671</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>672</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>656</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>657</v>
+        <v>673</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>674</v>
       </c>
       <c r="J1" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="2" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>660</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="M1" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>665</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>676</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>677</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>678</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="6" t="s">
         <v>669</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="N2" s="6" t="s">
         <v>670</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>671</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>601</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>664</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="L3" s="8"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="L4" s="8"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="L5" s="8"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="L6" s="8"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="L7" s="8"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="L8" s="8"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="L9" s="8"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="L10" s="8"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="L11" s="8"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="L12" s="8"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="L13" s="8"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="L14" s="8"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="L15" s="8"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="L16" s="8"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="L17" s="8"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="L18" s="8"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="L19" s="8"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="L20" s="8"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="L21" s="8"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="L22" s="8"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="L23" s="8"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="L24" s="8"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="L25" s="8"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="L26" s="8"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="L27" s="8"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="L28" s="8"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="L29" s="8"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="L30" s="8"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="L31" s="8"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="L32" s="8"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="L33" s="8"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="L34" s="8"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="L35" s="8"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="L36" s="8"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="L37" s="8"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="I38" s="8"/>
+      <c r="L38" s="8"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="L39" s="8"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="L40" s="8"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="L41" s="8"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C42" s="8"/>
+      <c r="G42" s="8"/>
+      <c r="I42" s="8"/>
+      <c r="L42" s="8"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C43" s="8"/>
+      <c r="G43" s="8"/>
+      <c r="I43" s="8"/>
+      <c r="L43" s="8"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="I44" s="8"/>
+      <c r="L44" s="8"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C45" s="8"/>
+      <c r="G45" s="8"/>
+      <c r="I45" s="8"/>
+      <c r="L45" s="8"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C46" s="8"/>
+      <c r="G46" s="8"/>
+      <c r="I46" s="8"/>
+      <c r="L46" s="8"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="I47" s="8"/>
+      <c r="L47" s="8"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C48" s="8"/>
+      <c r="G48" s="8"/>
+      <c r="I48" s="8"/>
+      <c r="L48" s="8"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C49" s="8"/>
+      <c r="G49" s="8"/>
+      <c r="I49" s="8"/>
+      <c r="L49" s="8"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C50" s="8"/>
+      <c r="G50" s="8"/>
+      <c r="I50" s="8"/>
+      <c r="L50" s="8"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="L51" s="8"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="L52" s="8"/>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="L53" s="8"/>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C54" s="8"/>
+      <c r="G54" s="8"/>
+      <c r="I54" s="8"/>
+      <c r="L54" s="8"/>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C55" s="8"/>
+      <c r="G55" s="8"/>
+      <c r="I55" s="8"/>
+      <c r="L55" s="8"/>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C56" s="8"/>
+      <c r="G56" s="8"/>
+      <c r="I56" s="8"/>
+      <c r="L56" s="8"/>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C57" s="8"/>
+      <c r="G57" s="8"/>
+      <c r="I57" s="8"/>
+      <c r="L57" s="8"/>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C58" s="8"/>
+      <c r="G58" s="8"/>
+      <c r="I58" s="8"/>
+      <c r="L58" s="8"/>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C59" s="8"/>
+      <c r="G59" s="8"/>
+      <c r="I59" s="8"/>
+      <c r="L59" s="8"/>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C60" s="8"/>
+      <c r="G60" s="8"/>
+      <c r="I60" s="8"/>
+      <c r="L60" s="8"/>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C61" s="8"/>
+      <c r="G61" s="8"/>
+      <c r="I61" s="8"/>
+      <c r="L61" s="8"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C62" s="8"/>
+      <c r="G62" s="8"/>
+      <c r="I62" s="8"/>
+      <c r="L62" s="8"/>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C63" s="8"/>
+      <c r="G63" s="8"/>
+      <c r="I63" s="8"/>
+      <c r="L63" s="8"/>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C64" s="8"/>
+      <c r="G64" s="8"/>
+      <c r="I64" s="8"/>
+      <c r="L64" s="8"/>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C65" s="8"/>
+      <c r="G65" s="8"/>
+      <c r="I65" s="8"/>
+      <c r="L65" s="8"/>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C66" s="8"/>
+      <c r="G66" s="8"/>
+      <c r="I66" s="8"/>
+      <c r="L66" s="8"/>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C67" s="8"/>
+      <c r="G67" s="8"/>
+      <c r="I67" s="8"/>
+      <c r="L67" s="8"/>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C68" s="8"/>
+      <c r="G68" s="8"/>
+      <c r="I68" s="8"/>
+      <c r="L68" s="8"/>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C69" s="8"/>
+      <c r="G69" s="8"/>
+      <c r="I69" s="8"/>
+      <c r="L69" s="8"/>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C70" s="8"/>
+      <c r="G70" s="8"/>
+      <c r="I70" s="8"/>
+      <c r="L70" s="8"/>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C71" s="8"/>
+      <c r="G71" s="8"/>
+      <c r="I71" s="8"/>
+      <c r="L71" s="8"/>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C72" s="8"/>
+      <c r="G72" s="8"/>
+      <c r="I72" s="8"/>
+      <c r="L72" s="8"/>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C73" s="8"/>
+      <c r="G73" s="8"/>
+      <c r="I73" s="8"/>
+      <c r="L73" s="8"/>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C74" s="8"/>
+      <c r="G74" s="8"/>
+      <c r="I74" s="8"/>
+      <c r="L74" s="8"/>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C75" s="8"/>
+      <c r="G75" s="8"/>
+      <c r="I75" s="8"/>
+      <c r="L75" s="8"/>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C76" s="8"/>
+      <c r="G76" s="8"/>
+      <c r="I76" s="8"/>
+      <c r="L76" s="8"/>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C77" s="8"/>
+      <c r="G77" s="8"/>
+      <c r="I77" s="8"/>
+      <c r="L77" s="8"/>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C78" s="8"/>
+      <c r="G78" s="8"/>
+      <c r="I78" s="8"/>
+      <c r="L78" s="8"/>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C79" s="8"/>
+      <c r="G79" s="8"/>
+      <c r="I79" s="8"/>
+      <c r="L79" s="8"/>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C80" s="8"/>
+      <c r="G80" s="8"/>
+      <c r="I80" s="8"/>
+      <c r="L80" s="8"/>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C81" s="8"/>
+      <c r="G81" s="8"/>
+      <c r="I81" s="8"/>
+      <c r="L81" s="8"/>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C82" s="8"/>
+      <c r="G82" s="8"/>
+      <c r="I82" s="8"/>
+      <c r="L82" s="8"/>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C83" s="8"/>
+      <c r="G83" s="8"/>
+      <c r="I83" s="8"/>
+      <c r="L83" s="8"/>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C84" s="8"/>
+      <c r="G84" s="8"/>
+      <c r="I84" s="8"/>
+      <c r="L84" s="8"/>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C85" s="8"/>
+      <c r="G85" s="8"/>
+      <c r="I85" s="8"/>
+      <c r="L85" s="8"/>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C86" s="8"/>
+      <c r="G86" s="8"/>
+      <c r="I86" s="8"/>
+      <c r="L86" s="8"/>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C87" s="8"/>
+      <c r="G87" s="8"/>
+      <c r="I87" s="8"/>
+      <c r="L87" s="8"/>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C88" s="8"/>
+      <c r="G88" s="8"/>
+      <c r="I88" s="8"/>
+      <c r="L88" s="8"/>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C89" s="8"/>
+      <c r="G89" s="8"/>
+      <c r="I89" s="8"/>
+      <c r="L89" s="8"/>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C90" s="8"/>
+      <c r="G90" s="8"/>
+      <c r="I90" s="8"/>
+      <c r="L90" s="8"/>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C91" s="8"/>
+      <c r="G91" s="8"/>
+      <c r="I91" s="8"/>
+      <c r="L91" s="8"/>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C92" s="8"/>
+      <c r="G92" s="8"/>
+      <c r="I92" s="8"/>
+      <c r="L92" s="8"/>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C93" s="8"/>
+      <c r="G93" s="8"/>
+      <c r="I93" s="8"/>
+      <c r="L93" s="8"/>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C94" s="8"/>
+      <c r="G94" s="8"/>
+      <c r="I94" s="8"/>
+      <c r="L94" s="8"/>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C95" s="8"/>
+      <c r="G95" s="8"/>
+      <c r="I95" s="8"/>
+      <c r="L95" s="8"/>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C96" s="8"/>
+      <c r="G96" s="8"/>
+      <c r="I96" s="8"/>
+      <c r="L96" s="8"/>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C97" s="8"/>
+      <c r="G97" s="8"/>
+      <c r="I97" s="8"/>
+      <c r="L97" s="8"/>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C98" s="8"/>
+      <c r="G98" s="8"/>
+      <c r="I98" s="8"/>
+      <c r="L98" s="8"/>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C99" s="8"/>
+      <c r="G99" s="8"/>
+      <c r="I99" s="8"/>
+      <c r="L99" s="8"/>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C100" s="8"/>
+      <c r="G100" s="8"/>
+      <c r="I100" s="8"/>
+      <c r="L100" s="8"/>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C101" s="8"/>
+      <c r="G101" s="8"/>
+      <c r="I101" s="8"/>
+      <c r="L101" s="8"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J2"/>
+  <autoFilter ref="A1:N2"/>
   <dataValidations count="10">
     <dataValidation type="list" showInputMessage="1" promptTitle="Source" prompt="請選擇 Fo Guang University" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="A10:A101">
       <formula1>"Fo Guang University"</formula1>
@@ -5740,28 +6837,28 @@
     <dataValidation type="list" showInputMessage="1" promptTitle="Source" prompt="請選擇 Fo Guang University" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="A2:A101">
       <formula1>"Fo Guang University"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Title" prompt="請選擇稱謂" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="B10:B101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Title" prompt="請選擇稱謂；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="B10:B101">
       <formula1>'稱謂'!$A$2:$A$11</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Title" prompt="請選擇稱謂" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="B2:B101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Title" prompt="請選擇稱謂；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="B2:B101">
       <formula1>'稱謂'!$A$2:$A$11</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Position" prompt="請選擇雇主職位" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="E10:E101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Position" prompt="請選擇雇主職位；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="F10:F101">
       <formula1>'雇主職位'!$A$2:$A$12</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Position" prompt="請選擇雇主職位" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="E2:E101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Position" prompt="請選擇雇主職位；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="F2:F101">
       <formula1>'雇主職位'!$A$2:$A$12</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Industry" prompt="請選擇產業" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="F10:F101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Industry" prompt="請選擇產業；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="H10:H101">
       <formula1>'產業'!$A$2:$A$29</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Industry" prompt="請選擇產業" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="F2:F101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Industry" prompt="請選擇產業；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="H2:H101">
       <formula1>'產業'!$A$2:$A$29</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Country" prompt="請選擇國家或地區" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="H10:H101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Country" prompt="請選擇國家或地區；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="K10:K101">
       <formula1>'國家或地區'!$A$2:$A$198</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Country" prompt="請選擇國家或地區" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="H2:H101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Country" prompt="請選擇國家或地區；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="K2:K101">
       <formula1>'國家或地區'!$A$2:$A$198</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/templates/QS_聯絡人匯入樣板.xlsx
+++ b/public/templates/QS_聯絡人匯入樣板.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="672">
   <si>
     <t>QS 聯絡人匯入樣板 — 填寫說明</t>
   </si>
@@ -39,7 +39,7 @@
     <t>二、工作表說明</t>
   </si>
   <si>
-    <t>• 「學術聯絡人」「雇主聯絡人」：已為選項欄位設定下拉選單（點儲存格右側 ▼ 選擇）。</t>
+    <t>• 「學術聯絡人」「雇主聯絡人」：選項欄位有下拉提示（▼），也可直接輸入；選單外文字匯入時會自動視為 Other。</t>
   </si>
   <si>
     <t>• 灰色斜體列為範例，填寫前請刪除；可從第 2 列起填寫，最多 100 筆。</t>
@@ -48,16 +48,13 @@
     <t>• 其他分頁為選項對照表（下拉選單來源），亦可手動查閱。</t>
   </si>
   <si>
-    <t>• 黃色欄位為「Other 說明」：下拉選單選 Other 後，在旁邊黃色欄自行填寫（不必改下拉選單那一格）。</t>
-  </si>
-  <si>
     <t>三、共通規則</t>
   </si>
   <si>
     <t>• Source 請選 Fo Guang University。</t>
   </si>
   <si>
-    <t>• Title／職稱／產業／學科／國家等用下拉選單；選 Other 時在右邊黃色欄填寫。</t>
+    <t>• Title／職稱／產業／學科／國家等：可從下拉選擇，或直接輸入自訂內容（系統會自動當作 Other）。</t>
   </si>
   <si>
     <t>• 姓名、系所、機構、Email、電話請手動輸入。</t>
@@ -1977,10 +1974,6 @@
     <t>Title</t>
   </si>
   <si>
-    <t xml:space="preserve">Title Other
-（選 Other 時填）</t>
-  </si>
-  <si>
     <t>First Name</t>
   </si>
   <si>
@@ -1990,10 +1983,6 @@
     <t>Job Title</t>
   </si>
   <si>
-    <t xml:space="preserve">Job Title Other
-（選 Other 時填）</t>
-  </si>
-  <si>
     <t>Department</t>
   </si>
   <si>
@@ -2003,20 +1992,12 @@
     <t>Country or Territory</t>
   </si>
   <si>
-    <t xml:space="preserve">Country Other
-（選 Other 時填）</t>
-  </si>
-  <si>
     <t>Email</t>
   </si>
   <si>
     <t>Subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Subject Other
-（選 Other 時填）</t>
-  </si>
-  <si>
     <t>Phone (Optional)</t>
   </si>
   <si>
@@ -2041,15 +2022,7 @@
     <t>Position</t>
   </si>
   <si>
-    <t xml:space="preserve">Position Other
-（選 Other 時填）</t>
-  </si>
-  <si>
     <t>Industry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Industry Other
-（選 Other 時填）</t>
   </si>
   <si>
     <t>Company Name</t>
@@ -2105,7 +2078,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2115,16 +2088,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1D4ED8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDE68A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFBEB"/>
       </patternFill>
     </fill>
   </fills>
@@ -2155,7 +2118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2165,16 +2128,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2517,7 +2473,7 @@
   <sheetPr>
     <tabColor rgb="FF64748B"/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="95" customWidth="1"/>
@@ -2575,12 +2531,12 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -2610,12 +2566,12 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
@@ -2625,17 +2581,12 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -2657,90 +2608,90 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -2764,130 +2715,130 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>48</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -2911,98 +2862,98 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>74</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>76</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>82</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>84</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -3026,234 +2977,234 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>92</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>98</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>102</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>104</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>108</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>110</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>116</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>120</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>124</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>126</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>132</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>134</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>136</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>140</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -3277,490 +3228,490 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>144</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>146</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>148</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>150</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>152</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>156</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>162</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>164</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>166</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>168</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>170</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>172</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>174</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>176</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>178</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>180</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>183</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>185</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>189</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>191</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>193</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B29" s="4" t="s">
         <v>195</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>197</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B31" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>201</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B33" s="4" t="s">
         <v>203</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B34" s="4" t="s">
         <v>205</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>207</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>209</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B38" s="4" t="s">
         <v>212</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B39" s="4" t="s">
         <v>214</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B40" s="4" t="s">
         <v>216</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B41" s="4" t="s">
         <v>218</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B42" s="4" t="s">
         <v>220</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B43" s="4" t="s">
         <v>222</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B44" s="4" t="s">
         <v>224</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B45" s="4" t="s">
         <v>226</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B46" s="4" t="s">
         <v>228</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B47" s="4" t="s">
         <v>230</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B48" s="4" t="s">
         <v>232</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="B49" s="4" t="s">
         <v>234</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B51" s="4" t="s">
         <v>238</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B52" s="4" t="s">
         <v>240</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B53" s="4" t="s">
         <v>242</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B54" s="4" t="s">
         <v>244</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B55" s="4" t="s">
         <v>246</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B56" s="4" t="s">
         <v>248</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B57" s="4" t="s">
         <v>250</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B58" s="4" t="s">
         <v>252</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B59" s="4" t="s">
         <v>254</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B60" s="4" t="s">
         <v>256</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -3784,1586 +3735,1586 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>258</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>260</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>262</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>264</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>266</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>268</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>270</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>272</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>274</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>276</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>278</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>280</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>282</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>284</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>286</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>288</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>290</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>292</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>294</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>296</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>298</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>300</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>302</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>304</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>306</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>308</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>310</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="B29" s="4" t="s">
         <v>312</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>314</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="B31" s="4" t="s">
         <v>316</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>318</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B33" s="4" t="s">
         <v>320</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="B34" s="4" t="s">
         <v>322</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>324</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>326</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="B37" s="4" t="s">
         <v>328</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="B38" s="4" t="s">
         <v>330</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="B39" s="4" t="s">
         <v>332</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="B40" s="4" t="s">
         <v>334</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="B41" s="4" t="s">
         <v>336</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="B42" s="4" t="s">
         <v>338</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="B43" s="4" t="s">
         <v>340</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="B44" s="4" t="s">
         <v>342</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="B45" s="4" t="s">
         <v>344</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="B46" s="4" t="s">
         <v>346</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="B47" s="4" t="s">
         <v>348</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="B48" s="4" t="s">
         <v>350</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="B49" s="4" t="s">
         <v>352</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>354</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="B51" s="4" t="s">
         <v>356</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="B52" s="4" t="s">
         <v>358</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="B53" s="4" t="s">
         <v>360</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="B54" s="4" t="s">
         <v>362</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="B55" s="4" t="s">
         <v>364</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="B56" s="4" t="s">
         <v>366</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B57" s="4" t="s">
         <v>368</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="B58" s="4" t="s">
         <v>370</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="B59" s="4" t="s">
         <v>372</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B60" s="4" t="s">
         <v>374</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="B61" s="4" t="s">
         <v>376</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="B62" s="4" t="s">
         <v>378</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="B63" s="4" t="s">
         <v>380</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="B64" s="4" t="s">
         <v>382</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="B65" s="4" t="s">
         <v>384</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="B66" s="4" t="s">
         <v>386</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="B67" s="4" t="s">
         <v>388</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B68" s="4" t="s">
         <v>390</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="B69" s="4" t="s">
         <v>392</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="B70" s="4" t="s">
         <v>394</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="B71" s="4" t="s">
         <v>396</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="B72" s="4" t="s">
         <v>398</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="B73" s="4" t="s">
         <v>400</v>
-      </c>
-      <c r="B73" s="4" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="B74" s="4" t="s">
         <v>402</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="B75" s="4" t="s">
         <v>404</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="B76" s="4" t="s">
         <v>406</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="B77" s="4" t="s">
         <v>408</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="B78" s="4" t="s">
         <v>410</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="B79" s="4" t="s">
         <v>412</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="B80" s="4" t="s">
         <v>414</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="B81" s="4" t="s">
         <v>416</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="B82" s="4" t="s">
         <v>418</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="B83" s="4" t="s">
         <v>420</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="B84" s="4" t="s">
         <v>422</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="B85" s="4" t="s">
         <v>424</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="B86" s="4" t="s">
         <v>426</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="B87" s="4" t="s">
         <v>428</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="B88" s="4" t="s">
         <v>430</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="B89" s="4" t="s">
         <v>432</v>
-      </c>
-      <c r="B89" s="4" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="B90" s="4" t="s">
         <v>434</v>
-      </c>
-      <c r="B90" s="4" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="B91" s="4" t="s">
         <v>436</v>
-      </c>
-      <c r="B91" s="4" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="B92" s="4" t="s">
         <v>438</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="B93" s="4" t="s">
         <v>440</v>
-      </c>
-      <c r="B93" s="4" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="B94" s="4" t="s">
         <v>442</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="B95" s="4" t="s">
         <v>444</v>
-      </c>
-      <c r="B95" s="4" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="B96" s="4" t="s">
         <v>446</v>
-      </c>
-      <c r="B96" s="4" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="B97" s="4" t="s">
         <v>448</v>
-      </c>
-      <c r="B97" s="4" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="B98" s="4" t="s">
         <v>450</v>
-      </c>
-      <c r="B98" s="4" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="B99" s="4" t="s">
         <v>452</v>
-      </c>
-      <c r="B99" s="4" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="B100" s="4" t="s">
         <v>454</v>
-      </c>
-      <c r="B100" s="4" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="B101" s="4" t="s">
         <v>456</v>
-      </c>
-      <c r="B101" s="4" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="B102" s="4" t="s">
         <v>458</v>
-      </c>
-      <c r="B102" s="4" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="B103" s="4" t="s">
         <v>460</v>
-      </c>
-      <c r="B103" s="4" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="B104" s="4" t="s">
         <v>462</v>
-      </c>
-      <c r="B104" s="4" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="B105" s="4" t="s">
         <v>464</v>
-      </c>
-      <c r="B105" s="4" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="B106" s="4" t="s">
         <v>466</v>
-      </c>
-      <c r="B106" s="4" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="B107" s="4" t="s">
         <v>468</v>
-      </c>
-      <c r="B107" s="4" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="B108" s="4" t="s">
         <v>470</v>
-      </c>
-      <c r="B108" s="4" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="B109" s="4" t="s">
         <v>472</v>
-      </c>
-      <c r="B109" s="4" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="B110" s="4" t="s">
         <v>474</v>
-      </c>
-      <c r="B110" s="4" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="B111" s="4" t="s">
         <v>476</v>
-      </c>
-      <c r="B111" s="4" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="B112" s="4" t="s">
         <v>478</v>
-      </c>
-      <c r="B112" s="4" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="B113" s="4" t="s">
         <v>480</v>
-      </c>
-      <c r="B113" s="4" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="B114" s="4" t="s">
         <v>482</v>
-      </c>
-      <c r="B114" s="4" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="B115" s="4" t="s">
         <v>484</v>
-      </c>
-      <c r="B115" s="4" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="B116" s="4" t="s">
         <v>486</v>
-      </c>
-      <c r="B116" s="4" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="B117" s="4" t="s">
         <v>488</v>
-      </c>
-      <c r="B117" s="4" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="B118" s="4" t="s">
         <v>490</v>
-      </c>
-      <c r="B118" s="4" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="B119" s="4" t="s">
         <v>492</v>
-      </c>
-      <c r="B119" s="4" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="B120" s="4" t="s">
         <v>494</v>
-      </c>
-      <c r="B120" s="4" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="B121" s="4" t="s">
         <v>496</v>
-      </c>
-      <c r="B121" s="4" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="B122" s="4" t="s">
         <v>498</v>
-      </c>
-      <c r="B122" s="4" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="B123" s="4" t="s">
         <v>500</v>
-      </c>
-      <c r="B123" s="4" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="B124" s="4" t="s">
         <v>502</v>
-      </c>
-      <c r="B124" s="4" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="B125" s="4" t="s">
         <v>504</v>
-      </c>
-      <c r="B125" s="4" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="B126" s="4" t="s">
         <v>506</v>
-      </c>
-      <c r="B126" s="4" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="B127" s="4" t="s">
         <v>508</v>
-      </c>
-      <c r="B127" s="4" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="B128" s="4" t="s">
         <v>510</v>
-      </c>
-      <c r="B128" s="4" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="B129" s="4" t="s">
         <v>512</v>
-      </c>
-      <c r="B129" s="4" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="B130" s="4" t="s">
         <v>514</v>
-      </c>
-      <c r="B130" s="4" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="B131" s="4" t="s">
         <v>516</v>
-      </c>
-      <c r="B131" s="4" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="B132" s="4" t="s">
         <v>518</v>
-      </c>
-      <c r="B132" s="4" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="B133" s="4" t="s">
         <v>520</v>
-      </c>
-      <c r="B133" s="4" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="B134" s="4" t="s">
         <v>522</v>
-      </c>
-      <c r="B134" s="4" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="B135" s="4" t="s">
         <v>524</v>
-      </c>
-      <c r="B135" s="4" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="B136" s="4" t="s">
         <v>526</v>
-      </c>
-      <c r="B136" s="4" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="B137" s="4" t="s">
         <v>528</v>
-      </c>
-      <c r="B137" s="4" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="B138" s="4" t="s">
         <v>530</v>
-      </c>
-      <c r="B138" s="4" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="B139" s="4" t="s">
         <v>532</v>
-      </c>
-      <c r="B139" s="4" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="B140" s="4" t="s">
         <v>534</v>
-      </c>
-      <c r="B140" s="4" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="B141" s="4" t="s">
         <v>536</v>
-      </c>
-      <c r="B141" s="4" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="B142" s="4" t="s">
         <v>538</v>
-      </c>
-      <c r="B142" s="4" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="B143" s="4" t="s">
         <v>540</v>
-      </c>
-      <c r="B143" s="4" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="B144" s="4" t="s">
         <v>542</v>
-      </c>
-      <c r="B144" s="4" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="B145" s="4" t="s">
         <v>544</v>
-      </c>
-      <c r="B145" s="4" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="B146" s="4" t="s">
         <v>546</v>
-      </c>
-      <c r="B146" s="4" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="B147" s="4" t="s">
         <v>548</v>
-      </c>
-      <c r="B147" s="4" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="B148" s="4" t="s">
         <v>550</v>
-      </c>
-      <c r="B148" s="4" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="B149" s="4" t="s">
         <v>552</v>
-      </c>
-      <c r="B149" s="4" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="B150" s="4" t="s">
         <v>554</v>
-      </c>
-      <c r="B150" s="4" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="B151" s="4" t="s">
         <v>556</v>
-      </c>
-      <c r="B151" s="4" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="B152" s="4" t="s">
         <v>558</v>
-      </c>
-      <c r="B152" s="4" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="B153" s="4" t="s">
         <v>560</v>
-      </c>
-      <c r="B153" s="4" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="B154" s="4" t="s">
         <v>562</v>
-      </c>
-      <c r="B154" s="4" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="B155" s="4" t="s">
         <v>564</v>
-      </c>
-      <c r="B155" s="4" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="B156" s="4" t="s">
         <v>566</v>
-      </c>
-      <c r="B156" s="4" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="B157" s="4" t="s">
         <v>568</v>
-      </c>
-      <c r="B157" s="4" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="B158" s="4" t="s">
         <v>570</v>
-      </c>
-      <c r="B158" s="4" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="B159" s="4" t="s">
         <v>572</v>
-      </c>
-      <c r="B159" s="4" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="B160" s="4" t="s">
         <v>574</v>
-      </c>
-      <c r="B160" s="4" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="B161" s="4" t="s">
         <v>576</v>
-      </c>
-      <c r="B161" s="4" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="B162" s="4" t="s">
         <v>578</v>
-      </c>
-      <c r="B162" s="4" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="B163" s="4" t="s">
         <v>580</v>
-      </c>
-      <c r="B163" s="4" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="B164" s="4" t="s">
         <v>582</v>
-      </c>
-      <c r="B164" s="4" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="B165" s="4" t="s">
         <v>584</v>
-      </c>
-      <c r="B165" s="4" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="B166" s="4" t="s">
         <v>586</v>
-      </c>
-      <c r="B166" s="4" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="B167" s="4" t="s">
         <v>588</v>
-      </c>
-      <c r="B167" s="4" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="B168" s="4" t="s">
         <v>590</v>
-      </c>
-      <c r="B168" s="4" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="B169" s="4" t="s">
         <v>592</v>
-      </c>
-      <c r="B169" s="4" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="B170" s="4" t="s">
         <v>594</v>
-      </c>
-      <c r="B170" s="4" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="B171" s="4" t="s">
         <v>596</v>
-      </c>
-      <c r="B171" s="4" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="B172" s="4" t="s">
         <v>598</v>
-      </c>
-      <c r="B172" s="4" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="B173" s="4" t="s">
         <v>600</v>
-      </c>
-      <c r="B173" s="4" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="B174" s="4" t="s">
         <v>602</v>
-      </c>
-      <c r="B174" s="4" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="B175" s="4" t="s">
         <v>604</v>
-      </c>
-      <c r="B175" s="4" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="B176" s="4" t="s">
         <v>606</v>
-      </c>
-      <c r="B176" s="4" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="B177" s="4" t="s">
         <v>608</v>
-      </c>
-      <c r="B177" s="4" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="B178" s="4" t="s">
         <v>610</v>
-      </c>
-      <c r="B178" s="4" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="B179" s="4" t="s">
         <v>612</v>
-      </c>
-      <c r="B179" s="4" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="B180" s="4" t="s">
         <v>614</v>
-      </c>
-      <c r="B180" s="4" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="B181" s="4" t="s">
         <v>616</v>
-      </c>
-      <c r="B181" s="4" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="B182" s="4" t="s">
         <v>618</v>
-      </c>
-      <c r="B182" s="4" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="B183" s="4" t="s">
         <v>620</v>
-      </c>
-      <c r="B183" s="4" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="184" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="B184" s="4" t="s">
         <v>622</v>
-      </c>
-      <c r="B184" s="4" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="185" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="B185" s="4" t="s">
         <v>624</v>
-      </c>
-      <c r="B185" s="4" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="186" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="B186" s="4" t="s">
         <v>626</v>
-      </c>
-      <c r="B186" s="4" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="187" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="B187" s="4" t="s">
         <v>628</v>
-      </c>
-      <c r="B187" s="4" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="188" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="B188" s="4" t="s">
         <v>630</v>
-      </c>
-      <c r="B188" s="4" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="189" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="B189" s="4" t="s">
         <v>632</v>
-      </c>
-      <c r="B189" s="4" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="190" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="B190" s="4" t="s">
         <v>634</v>
-      </c>
-      <c r="B190" s="4" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="191" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="B191" s="4" t="s">
         <v>636</v>
-      </c>
-      <c r="B191" s="4" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="B192" s="4" t="s">
         <v>638</v>
-      </c>
-      <c r="B192" s="4" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="B193" s="4" t="s">
         <v>640</v>
-      </c>
-      <c r="B193" s="4" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="194" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="B194" s="4" t="s">
         <v>642</v>
-      </c>
-      <c r="B194" s="4" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="195" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
+        <v>643</v>
+      </c>
+      <c r="B195" s="4" t="s">
         <v>644</v>
-      </c>
-      <c r="B195" s="4" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="196" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="B196" s="4" t="s">
         <v>646</v>
-      </c>
-      <c r="B196" s="4" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="197" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="B197" s="4" t="s">
         <v>648</v>
-      </c>
-      <c r="B197" s="4" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="198" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B198" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="B198" s="4" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -5378,744 +5329,220 @@
   <sheetPr>
     <tabColor rgb="FFDC2626"/>
   </sheetPr>
-  <dimension ref="A1:O101"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="4" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="31" customWidth="1"/>
-    <col min="7" max="7" width="25" customWidth="1"/>
-    <col min="8" max="8" width="23" customWidth="1"/>
-    <col min="9" max="9" width="21" customWidth="1"/>
-    <col min="10" max="10" width="22" customWidth="1"/>
-    <col min="11" max="11" width="23" customWidth="1"/>
-    <col min="12" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="23" customWidth="1"/>
-    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="2" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="31" customWidth="1"/>
+    <col min="6" max="6" width="23" customWidth="1"/>
+    <col min="7" max="7" width="21" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>650</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>651</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="3" t="s">
         <v>652</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>653</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>654</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="3" t="s">
         <v>656</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>657</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>658</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="K1" s="5" t="s">
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>660</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="B2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>661</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="D2" s="5" t="s">
         <v>662</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="E2" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>663</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="G2" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="I2" s="5" t="s">
         <v>664</v>
       </c>
-    </row>
-    <row r="2" ht="20" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="J2" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="K2" s="5" t="s">
         <v>665</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>666</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>667</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>668</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>665</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>602</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>669</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="N3" s="8"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="N4" s="8"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="N5" s="8"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="N6" s="8"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="N7" s="8"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="N8" s="8"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="N9" s="8"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="N10" s="8"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="N11" s="8"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="N12" s="8"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="N13" s="8"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="N14" s="8"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="N15" s="8"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="N16" s="8"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="N17" s="8"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="N18" s="8"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="N19" s="8"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="N20" s="8"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="N21" s="8"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="K22" s="8"/>
-      <c r="N22" s="8"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="K23" s="8"/>
-      <c r="N23" s="8"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="N24" s="8"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="N25" s="8"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="N26" s="8"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="K27" s="8"/>
-      <c r="N27" s="8"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="N28" s="8"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="K29" s="8"/>
-      <c r="N29" s="8"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="N30" s="8"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="K31" s="8"/>
-      <c r="N31" s="8"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="N32" s="8"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="K33" s="8"/>
-      <c r="N33" s="8"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="N34" s="8"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="K35" s="8"/>
-      <c r="N35" s="8"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="N36" s="8"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="K37" s="8"/>
-      <c r="N37" s="8"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C38" s="8"/>
-      <c r="G38" s="8"/>
-      <c r="K38" s="8"/>
-      <c r="N38" s="8"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="K39" s="8"/>
-      <c r="N39" s="8"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C40" s="8"/>
-      <c r="G40" s="8"/>
-      <c r="K40" s="8"/>
-      <c r="N40" s="8"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C41" s="8"/>
-      <c r="G41" s="8"/>
-      <c r="K41" s="8"/>
-      <c r="N41" s="8"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C42" s="8"/>
-      <c r="G42" s="8"/>
-      <c r="K42" s="8"/>
-      <c r="N42" s="8"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C43" s="8"/>
-      <c r="G43" s="8"/>
-      <c r="K43" s="8"/>
-      <c r="N43" s="8"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C44" s="8"/>
-      <c r="G44" s="8"/>
-      <c r="K44" s="8"/>
-      <c r="N44" s="8"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C45" s="8"/>
-      <c r="G45" s="8"/>
-      <c r="K45" s="8"/>
-      <c r="N45" s="8"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C46" s="8"/>
-      <c r="G46" s="8"/>
-      <c r="K46" s="8"/>
-      <c r="N46" s="8"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C47" s="8"/>
-      <c r="G47" s="8"/>
-      <c r="K47" s="8"/>
-      <c r="N47" s="8"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C48" s="8"/>
-      <c r="G48" s="8"/>
-      <c r="K48" s="8"/>
-      <c r="N48" s="8"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C49" s="8"/>
-      <c r="G49" s="8"/>
-      <c r="K49" s="8"/>
-      <c r="N49" s="8"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C50" s="8"/>
-      <c r="G50" s="8"/>
-      <c r="K50" s="8"/>
-      <c r="N50" s="8"/>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C51" s="8"/>
-      <c r="G51" s="8"/>
-      <c r="K51" s="8"/>
-      <c r="N51" s="8"/>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C52" s="8"/>
-      <c r="G52" s="8"/>
-      <c r="K52" s="8"/>
-      <c r="N52" s="8"/>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C53" s="8"/>
-      <c r="G53" s="8"/>
-      <c r="K53" s="8"/>
-      <c r="N53" s="8"/>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C54" s="8"/>
-      <c r="G54" s="8"/>
-      <c r="K54" s="8"/>
-      <c r="N54" s="8"/>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C55" s="8"/>
-      <c r="G55" s="8"/>
-      <c r="K55" s="8"/>
-      <c r="N55" s="8"/>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C56" s="8"/>
-      <c r="G56" s="8"/>
-      <c r="K56" s="8"/>
-      <c r="N56" s="8"/>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C57" s="8"/>
-      <c r="G57" s="8"/>
-      <c r="K57" s="8"/>
-      <c r="N57" s="8"/>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C58" s="8"/>
-      <c r="G58" s="8"/>
-      <c r="K58" s="8"/>
-      <c r="N58" s="8"/>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C59" s="8"/>
-      <c r="G59" s="8"/>
-      <c r="K59" s="8"/>
-      <c r="N59" s="8"/>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C60" s="8"/>
-      <c r="G60" s="8"/>
-      <c r="K60" s="8"/>
-      <c r="N60" s="8"/>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C61" s="8"/>
-      <c r="G61" s="8"/>
-      <c r="K61" s="8"/>
-      <c r="N61" s="8"/>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C62" s="8"/>
-      <c r="G62" s="8"/>
-      <c r="K62" s="8"/>
-      <c r="N62" s="8"/>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C63" s="8"/>
-      <c r="G63" s="8"/>
-      <c r="K63" s="8"/>
-      <c r="N63" s="8"/>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C64" s="8"/>
-      <c r="G64" s="8"/>
-      <c r="K64" s="8"/>
-      <c r="N64" s="8"/>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C65" s="8"/>
-      <c r="G65" s="8"/>
-      <c r="K65" s="8"/>
-      <c r="N65" s="8"/>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C66" s="8"/>
-      <c r="G66" s="8"/>
-      <c r="K66" s="8"/>
-      <c r="N66" s="8"/>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C67" s="8"/>
-      <c r="G67" s="8"/>
-      <c r="K67" s="8"/>
-      <c r="N67" s="8"/>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C68" s="8"/>
-      <c r="G68" s="8"/>
-      <c r="K68" s="8"/>
-      <c r="N68" s="8"/>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C69" s="8"/>
-      <c r="G69" s="8"/>
-      <c r="K69" s="8"/>
-      <c r="N69" s="8"/>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C70" s="8"/>
-      <c r="G70" s="8"/>
-      <c r="K70" s="8"/>
-      <c r="N70" s="8"/>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C71" s="8"/>
-      <c r="G71" s="8"/>
-      <c r="K71" s="8"/>
-      <c r="N71" s="8"/>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C72" s="8"/>
-      <c r="G72" s="8"/>
-      <c r="K72" s="8"/>
-      <c r="N72" s="8"/>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C73" s="8"/>
-      <c r="G73" s="8"/>
-      <c r="K73" s="8"/>
-      <c r="N73" s="8"/>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C74" s="8"/>
-      <c r="G74" s="8"/>
-      <c r="K74" s="8"/>
-      <c r="N74" s="8"/>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C75" s="8"/>
-      <c r="G75" s="8"/>
-      <c r="K75" s="8"/>
-      <c r="N75" s="8"/>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C76" s="8"/>
-      <c r="G76" s="8"/>
-      <c r="K76" s="8"/>
-      <c r="N76" s="8"/>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C77" s="8"/>
-      <c r="G77" s="8"/>
-      <c r="K77" s="8"/>
-      <c r="N77" s="8"/>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C78" s="8"/>
-      <c r="G78" s="8"/>
-      <c r="K78" s="8"/>
-      <c r="N78" s="8"/>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C79" s="8"/>
-      <c r="G79" s="8"/>
-      <c r="K79" s="8"/>
-      <c r="N79" s="8"/>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C80" s="8"/>
-      <c r="G80" s="8"/>
-      <c r="K80" s="8"/>
-      <c r="N80" s="8"/>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C81" s="8"/>
-      <c r="G81" s="8"/>
-      <c r="K81" s="8"/>
-      <c r="N81" s="8"/>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C82" s="8"/>
-      <c r="G82" s="8"/>
-      <c r="K82" s="8"/>
-      <c r="N82" s="8"/>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C83" s="8"/>
-      <c r="G83" s="8"/>
-      <c r="K83" s="8"/>
-      <c r="N83" s="8"/>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C84" s="8"/>
-      <c r="G84" s="8"/>
-      <c r="K84" s="8"/>
-      <c r="N84" s="8"/>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C85" s="8"/>
-      <c r="G85" s="8"/>
-      <c r="K85" s="8"/>
-      <c r="N85" s="8"/>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C86" s="8"/>
-      <c r="G86" s="8"/>
-      <c r="K86" s="8"/>
-      <c r="N86" s="8"/>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C87" s="8"/>
-      <c r="G87" s="8"/>
-      <c r="K87" s="8"/>
-      <c r="N87" s="8"/>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C88" s="8"/>
-      <c r="G88" s="8"/>
-      <c r="K88" s="8"/>
-      <c r="N88" s="8"/>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C89" s="8"/>
-      <c r="G89" s="8"/>
-      <c r="K89" s="8"/>
-      <c r="N89" s="8"/>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C90" s="8"/>
-      <c r="G90" s="8"/>
-      <c r="K90" s="8"/>
-      <c r="N90" s="8"/>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C91" s="8"/>
-      <c r="G91" s="8"/>
-      <c r="K91" s="8"/>
-      <c r="N91" s="8"/>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C92" s="8"/>
-      <c r="G92" s="8"/>
-      <c r="K92" s="8"/>
-      <c r="N92" s="8"/>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C93" s="8"/>
-      <c r="G93" s="8"/>
-      <c r="K93" s="8"/>
-      <c r="N93" s="8"/>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C94" s="8"/>
-      <c r="G94" s="8"/>
-      <c r="K94" s="8"/>
-      <c r="N94" s="8"/>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C95" s="8"/>
-      <c r="G95" s="8"/>
-      <c r="K95" s="8"/>
-      <c r="N95" s="8"/>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C96" s="8"/>
-      <c r="G96" s="8"/>
-      <c r="K96" s="8"/>
-      <c r="N96" s="8"/>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C97" s="8"/>
-      <c r="G97" s="8"/>
-      <c r="K97" s="8"/>
-      <c r="N97" s="8"/>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C98" s="8"/>
-      <c r="G98" s="8"/>
-      <c r="K98" s="8"/>
-      <c r="N98" s="8"/>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C99" s="8"/>
-      <c r="G99" s="8"/>
-      <c r="K99" s="8"/>
-      <c r="N99" s="8"/>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C100" s="8"/>
-      <c r="G100" s="8"/>
-      <c r="K100" s="8"/>
-      <c r="N100" s="8"/>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C101" s="8"/>
-      <c r="G101" s="8"/>
-      <c r="K101" s="8"/>
-      <c r="N101" s="8"/>
-    </row>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:O2"/>
+  <autoFilter ref="A1:K2"/>
   <dataValidations count="10">
-    <dataValidation type="list" showInputMessage="1" promptTitle="Source" prompt="請選擇 Fo Guang University" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="A10:A101">
+    <dataValidation type="list" showInputMessage="1" promptTitle="Source" prompt="請選擇 Fo Guang University" sqref="A10:A101">
       <formula1>"Fo Guang University"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" promptTitle="Source" prompt="請選擇 Fo Guang University" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="A2:A101">
+    <dataValidation type="list" showInputMessage="1" promptTitle="Source" prompt="請選擇 Fo Guang University" sqref="A2:A101">
       <formula1>"Fo Guang University"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Title" prompt="請選擇稱謂；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="B10:B101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Title" prompt="可選擇或輸入；選單外會自動視為 Other" sqref="B10:B101">
       <formula1>'稱謂'!$A$2:$A$11</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Title" prompt="請選擇稱謂；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="B2:B101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Title" prompt="可選擇或輸入；選單外會自動視為 Other" sqref="B2:B101">
       <formula1>'稱謂'!$A$2:$A$11</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Job Title" prompt="請選擇學術職稱；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="F10:F101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Job Title" prompt="可選擇或輸入；選單外會自動視為 Other" sqref="E10:E101">
       <formula1>'學術職稱'!$A$2:$A$16</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Job Title" prompt="請選擇學術職稱；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="F2:F101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Job Title" prompt="可選擇或輸入；選單外會自動視為 Other" sqref="E2:E101">
       <formula1>'學術職稱'!$A$2:$A$16</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Country" prompt="請選擇國家或地區；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="J10:J101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Country" prompt="可選擇或輸入；選單外會自動視為 Other" sqref="H10:H101">
       <formula1>'國家或地區'!$A$2:$A$198</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Country" prompt="請選擇國家或地區；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="J2:J101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Country" prompt="可選擇或輸入；選單外會自動視為 Other" sqref="H2:H101">
       <formula1>'國家或地區'!$A$2:$A$198</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Subject" prompt="請選擇學科領域；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="M10:M101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Subject" prompt="可選擇或輸入；選單外會自動視為 Other" sqref="J10:J101">
       <formula1>'學科領域'!$A$2:$A$61</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Subject" prompt="請選擇學科領域；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="M2:M101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Subject" prompt="可選擇或輸入；選單外會自動視為 Other" sqref="J2:J101">
       <formula1>'學科領域'!$A$2:$A$61</formula1>
     </dataValidation>
   </dataValidations>
@@ -6129,736 +5556,212 @@
   <sheetPr>
     <tabColor rgb="FFF59E0B"/>
   </sheetPr>
-  <dimension ref="A1:N101"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="4" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="19" customWidth="1"/>
-    <col min="7" max="7" width="24" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="24" customWidth="1"/>
-    <col min="10" max="11" width="22" customWidth="1"/>
-    <col min="12" max="12" width="23" customWidth="1"/>
-    <col min="13" max="13" width="15" customWidth="1"/>
-    <col min="14" max="14" width="18" customWidth="1"/>
+    <col min="2" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>650</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>651</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="3" t="s">
         <v>652</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>653</v>
-      </c>
       <c r="E1" s="3" t="s">
-        <v>654</v>
+        <v>666</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>669</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>670</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>671</v>
       </c>
-      <c r="G1" s="5" t="s">
-        <v>672</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>673</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>674</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>675</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>659</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>660</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>661</v>
-      </c>
-      <c r="N1" s="3" t="s">
+      <c r="H2" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="I2" s="5" t="s">
         <v>664</v>
       </c>
-    </row>
-    <row r="2" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="J2" s="5" t="s">
         <v>665</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>676</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>677</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>678</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>602</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>669</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="L3" s="8"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="L4" s="8"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="L5" s="8"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="L6" s="8"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="L7" s="8"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="L8" s="8"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="L9" s="8"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="L10" s="8"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="L11" s="8"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="L12" s="8"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="L13" s="8"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="L14" s="8"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="L15" s="8"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="L16" s="8"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="L17" s="8"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="L18" s="8"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="L19" s="8"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="L20" s="8"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="L21" s="8"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="L22" s="8"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="L23" s="8"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="L24" s="8"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="L25" s="8"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="L26" s="8"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="L27" s="8"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="L28" s="8"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="L29" s="8"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="L30" s="8"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="L31" s="8"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="I32" s="8"/>
-      <c r="L32" s="8"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="I33" s="8"/>
-      <c r="L33" s="8"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="I34" s="8"/>
-      <c r="L34" s="8"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="I35" s="8"/>
-      <c r="L35" s="8"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="I36" s="8"/>
-      <c r="L36" s="8"/>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="I37" s="8"/>
-      <c r="L37" s="8"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C38" s="8"/>
-      <c r="G38" s="8"/>
-      <c r="I38" s="8"/>
-      <c r="L38" s="8"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="I39" s="8"/>
-      <c r="L39" s="8"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C40" s="8"/>
-      <c r="G40" s="8"/>
-      <c r="I40" s="8"/>
-      <c r="L40" s="8"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C41" s="8"/>
-      <c r="G41" s="8"/>
-      <c r="I41" s="8"/>
-      <c r="L41" s="8"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C42" s="8"/>
-      <c r="G42" s="8"/>
-      <c r="I42" s="8"/>
-      <c r="L42" s="8"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C43" s="8"/>
-      <c r="G43" s="8"/>
-      <c r="I43" s="8"/>
-      <c r="L43" s="8"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C44" s="8"/>
-      <c r="G44" s="8"/>
-      <c r="I44" s="8"/>
-      <c r="L44" s="8"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C45" s="8"/>
-      <c r="G45" s="8"/>
-      <c r="I45" s="8"/>
-      <c r="L45" s="8"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C46" s="8"/>
-      <c r="G46" s="8"/>
-      <c r="I46" s="8"/>
-      <c r="L46" s="8"/>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C47" s="8"/>
-      <c r="G47" s="8"/>
-      <c r="I47" s="8"/>
-      <c r="L47" s="8"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C48" s="8"/>
-      <c r="G48" s="8"/>
-      <c r="I48" s="8"/>
-      <c r="L48" s="8"/>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C49" s="8"/>
-      <c r="G49" s="8"/>
-      <c r="I49" s="8"/>
-      <c r="L49" s="8"/>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C50" s="8"/>
-      <c r="G50" s="8"/>
-      <c r="I50" s="8"/>
-      <c r="L50" s="8"/>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C51" s="8"/>
-      <c r="G51" s="8"/>
-      <c r="I51" s="8"/>
-      <c r="L51" s="8"/>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C52" s="8"/>
-      <c r="G52" s="8"/>
-      <c r="I52" s="8"/>
-      <c r="L52" s="8"/>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C53" s="8"/>
-      <c r="G53" s="8"/>
-      <c r="I53" s="8"/>
-      <c r="L53" s="8"/>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C54" s="8"/>
-      <c r="G54" s="8"/>
-      <c r="I54" s="8"/>
-      <c r="L54" s="8"/>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C55" s="8"/>
-      <c r="G55" s="8"/>
-      <c r="I55" s="8"/>
-      <c r="L55" s="8"/>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C56" s="8"/>
-      <c r="G56" s="8"/>
-      <c r="I56" s="8"/>
-      <c r="L56" s="8"/>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C57" s="8"/>
-      <c r="G57" s="8"/>
-      <c r="I57" s="8"/>
-      <c r="L57" s="8"/>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C58" s="8"/>
-      <c r="G58" s="8"/>
-      <c r="I58" s="8"/>
-      <c r="L58" s="8"/>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C59" s="8"/>
-      <c r="G59" s="8"/>
-      <c r="I59" s="8"/>
-      <c r="L59" s="8"/>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C60" s="8"/>
-      <c r="G60" s="8"/>
-      <c r="I60" s="8"/>
-      <c r="L60" s="8"/>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C61" s="8"/>
-      <c r="G61" s="8"/>
-      <c r="I61" s="8"/>
-      <c r="L61" s="8"/>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C62" s="8"/>
-      <c r="G62" s="8"/>
-      <c r="I62" s="8"/>
-      <c r="L62" s="8"/>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C63" s="8"/>
-      <c r="G63" s="8"/>
-      <c r="I63" s="8"/>
-      <c r="L63" s="8"/>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C64" s="8"/>
-      <c r="G64" s="8"/>
-      <c r="I64" s="8"/>
-      <c r="L64" s="8"/>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C65" s="8"/>
-      <c r="G65" s="8"/>
-      <c r="I65" s="8"/>
-      <c r="L65" s="8"/>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C66" s="8"/>
-      <c r="G66" s="8"/>
-      <c r="I66" s="8"/>
-      <c r="L66" s="8"/>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C67" s="8"/>
-      <c r="G67" s="8"/>
-      <c r="I67" s="8"/>
-      <c r="L67" s="8"/>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C68" s="8"/>
-      <c r="G68" s="8"/>
-      <c r="I68" s="8"/>
-      <c r="L68" s="8"/>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C69" s="8"/>
-      <c r="G69" s="8"/>
-      <c r="I69" s="8"/>
-      <c r="L69" s="8"/>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C70" s="8"/>
-      <c r="G70" s="8"/>
-      <c r="I70" s="8"/>
-      <c r="L70" s="8"/>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C71" s="8"/>
-      <c r="G71" s="8"/>
-      <c r="I71" s="8"/>
-      <c r="L71" s="8"/>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C72" s="8"/>
-      <c r="G72" s="8"/>
-      <c r="I72" s="8"/>
-      <c r="L72" s="8"/>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C73" s="8"/>
-      <c r="G73" s="8"/>
-      <c r="I73" s="8"/>
-      <c r="L73" s="8"/>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C74" s="8"/>
-      <c r="G74" s="8"/>
-      <c r="I74" s="8"/>
-      <c r="L74" s="8"/>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C75" s="8"/>
-      <c r="G75" s="8"/>
-      <c r="I75" s="8"/>
-      <c r="L75" s="8"/>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C76" s="8"/>
-      <c r="G76" s="8"/>
-      <c r="I76" s="8"/>
-      <c r="L76" s="8"/>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C77" s="8"/>
-      <c r="G77" s="8"/>
-      <c r="I77" s="8"/>
-      <c r="L77" s="8"/>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C78" s="8"/>
-      <c r="G78" s="8"/>
-      <c r="I78" s="8"/>
-      <c r="L78" s="8"/>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C79" s="8"/>
-      <c r="G79" s="8"/>
-      <c r="I79" s="8"/>
-      <c r="L79" s="8"/>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C80" s="8"/>
-      <c r="G80" s="8"/>
-      <c r="I80" s="8"/>
-      <c r="L80" s="8"/>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C81" s="8"/>
-      <c r="G81" s="8"/>
-      <c r="I81" s="8"/>
-      <c r="L81" s="8"/>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C82" s="8"/>
-      <c r="G82" s="8"/>
-      <c r="I82" s="8"/>
-      <c r="L82" s="8"/>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C83" s="8"/>
-      <c r="G83" s="8"/>
-      <c r="I83" s="8"/>
-      <c r="L83" s="8"/>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C84" s="8"/>
-      <c r="G84" s="8"/>
-      <c r="I84" s="8"/>
-      <c r="L84" s="8"/>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C85" s="8"/>
-      <c r="G85" s="8"/>
-      <c r="I85" s="8"/>
-      <c r="L85" s="8"/>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C86" s="8"/>
-      <c r="G86" s="8"/>
-      <c r="I86" s="8"/>
-      <c r="L86" s="8"/>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C87" s="8"/>
-      <c r="G87" s="8"/>
-      <c r="I87" s="8"/>
-      <c r="L87" s="8"/>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C88" s="8"/>
-      <c r="G88" s="8"/>
-      <c r="I88" s="8"/>
-      <c r="L88" s="8"/>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C89" s="8"/>
-      <c r="G89" s="8"/>
-      <c r="I89" s="8"/>
-      <c r="L89" s="8"/>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C90" s="8"/>
-      <c r="G90" s="8"/>
-      <c r="I90" s="8"/>
-      <c r="L90" s="8"/>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C91" s="8"/>
-      <c r="G91" s="8"/>
-      <c r="I91" s="8"/>
-      <c r="L91" s="8"/>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C92" s="8"/>
-      <c r="G92" s="8"/>
-      <c r="I92" s="8"/>
-      <c r="L92" s="8"/>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C93" s="8"/>
-      <c r="G93" s="8"/>
-      <c r="I93" s="8"/>
-      <c r="L93" s="8"/>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C94" s="8"/>
-      <c r="G94" s="8"/>
-      <c r="I94" s="8"/>
-      <c r="L94" s="8"/>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C95" s="8"/>
-      <c r="G95" s="8"/>
-      <c r="I95" s="8"/>
-      <c r="L95" s="8"/>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C96" s="8"/>
-      <c r="G96" s="8"/>
-      <c r="I96" s="8"/>
-      <c r="L96" s="8"/>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C97" s="8"/>
-      <c r="G97" s="8"/>
-      <c r="I97" s="8"/>
-      <c r="L97" s="8"/>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C98" s="8"/>
-      <c r="G98" s="8"/>
-      <c r="I98" s="8"/>
-      <c r="L98" s="8"/>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C99" s="8"/>
-      <c r="G99" s="8"/>
-      <c r="I99" s="8"/>
-      <c r="L99" s="8"/>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C100" s="8"/>
-      <c r="G100" s="8"/>
-      <c r="I100" s="8"/>
-      <c r="L100" s="8"/>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C101" s="8"/>
-      <c r="G101" s="8"/>
-      <c r="I101" s="8"/>
-      <c r="L101" s="8"/>
-    </row>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:N2"/>
+  <autoFilter ref="A1:J2"/>
   <dataValidations count="10">
-    <dataValidation type="list" showInputMessage="1" promptTitle="Source" prompt="請選擇 Fo Guang University" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="A10:A101">
+    <dataValidation type="list" showInputMessage="1" promptTitle="Source" prompt="請選擇 Fo Guang University" sqref="A10:A101">
       <formula1>"Fo Guang University"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" promptTitle="Source" prompt="請選擇 Fo Guang University" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="A2:A101">
+    <dataValidation type="list" showInputMessage="1" promptTitle="Source" prompt="請選擇 Fo Guang University" sqref="A2:A101">
       <formula1>"Fo Guang University"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Title" prompt="請選擇稱謂；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="B10:B101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Title" prompt="可選擇或輸入；選單外會自動視為 Other" sqref="B10:B101">
       <formula1>'稱謂'!$A$2:$A$11</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Title" prompt="請選擇稱謂；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="B2:B101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Title" prompt="可選擇或輸入；選單外會自動視為 Other" sqref="B2:B101">
       <formula1>'稱謂'!$A$2:$A$11</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Position" prompt="請選擇雇主職位；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="F10:F101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Position" prompt="可選擇或輸入；選單外會自動視為 Other" sqref="E10:E101">
       <formula1>'雇主職位'!$A$2:$A$12</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Position" prompt="請選擇雇主職位；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="F2:F101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Position" prompt="可選擇或輸入；選單外會自動視為 Other" sqref="E2:E101">
       <formula1>'雇主職位'!$A$2:$A$12</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Industry" prompt="請選擇產業；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="H10:H101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Industry" prompt="可選擇或輸入；選單外會自動視為 Other" sqref="F10:F101">
       <formula1>'產業'!$A$2:$A$29</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Industry" prompt="請選擇產業；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="H2:H101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Industry" prompt="可選擇或輸入；選單外會自動視為 Other" sqref="F2:F101">
       <formula1>'產業'!$A$2:$A$29</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Country" prompt="請選擇國家或地區；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="K10:K101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Country" prompt="可選擇或輸入；選單外會自動視為 Other" sqref="H10:H101">
       <formula1>'國家或地區'!$A$2:$A$198</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Country" prompt="請選擇國家或地區；若選 Other 請在右邊黃色欄填寫" showErrorMessage="1" errorStyle="error" errorTitle="選項不正確" error="請從下拉選單選擇有效選項" sqref="K2:K101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Country" prompt="可選擇或輸入；選單外會自動視為 Other" sqref="H2:H101">
       <formula1>'國家或地區'!$A$2:$A$198</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/templates/QS_聯絡人匯入樣板.xlsx
+++ b/public/templates/QS_聯絡人匯入樣板.xlsx
@@ -42,7 +42,7 @@
     <t>• 「學術聯絡人」「雇主聯絡人」：選項欄位有下拉提示（▼），也可直接輸入；選單外文字匯入時會自動視為 Other。</t>
   </si>
   <si>
-    <t>• 灰色斜體列為範例，填寫前請刪除；可從第 2 列起填寫，最多 100 筆。</t>
+    <t>• 第 2 列為範例，填寫前請刪除；可從第 2 列起填寫，最多 100 筆。</t>
   </si>
   <si>
     <t>• 其他分頁為選項對照表（下拉選單來源），亦可手動查閱。</t>
@@ -3098,8 +3098,7 @@
   <si>
     <r>
       <rPr>
-        <i/>
-        <color rgb="FF64748B"/>
+        <color rgb="FF0F172A"/>
         <sz val="11"/>
         <rFont val="Times New Roman"/>
       </rPr>
@@ -3107,8 +3106,7 @@
     </r>
     <r>
       <rPr>
-        <i/>
-        <color rgb="FF64748B"/>
+        <color rgb="FF0F172A"/>
         <sz val="11"/>
         <rFont val="標楷體"/>
       </rPr>
@@ -3116,8 +3114,7 @@
     </r>
     <r>
       <rPr>
-        <i/>
-        <color rgb="FF64748B"/>
+        <color rgb="FF0F172A"/>
         <sz val="11"/>
         <rFont val="Times New Roman"/>
       </rPr>
@@ -3150,7 +3147,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -3188,12 +3185,6 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FF64748B"/>
       <sz val="11"/>
       <name val="Times New Roman"/>
     </font>
@@ -3238,7 +3229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3259,9 +3250,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6511,37 +6499,37 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="5" t="s">
         <v>660</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="5" t="s">
         <v>661</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="5" t="s">
         <v>662</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="5" t="s">
         <v>663</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="5" t="s">
         <v>660</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="5" t="s">
         <v>601</v>
       </c>
       <c r="I2" s="7" t="s">
         <v>664</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="5" t="s">
         <v>665</v>
       </c>
     </row>
@@ -10099,34 +10087,34 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="5" t="s">
         <v>660</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="5" t="s">
         <v>669</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="5" t="s">
         <v>670</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="5" t="s">
         <v>671</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="5" t="s">
         <v>601</v>
       </c>
       <c r="I2" s="7" t="s">
         <v>664</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="5" t="s">
         <v>665</v>
       </c>
     </row>

--- a/public/templates/QS_聯絡人匯入樣板.xlsx
+++ b/public/templates/QS_聯絡人匯入樣板.xlsx
@@ -33,7 +33,7 @@
     <t>本檔供各單位先離線整理聯絡人資料，欄位與線上提交系統／QS 官方格式一致。</t>
   </si>
   <si>
-    <t>填寫完成後，請至線上提交網站「從 Excel 匯入」上傳本檔；通過驗證後可匯入表單並提交。提交後若下載 Excel 備份，系統會自動套用中文標楷體／英文 Times New Roman。</t>
+    <t>填寫完成後，請至線上提交網站「從 Excel 匯入」上傳本檔；通過驗證後可匯入表單並提交。</t>
   </si>
   <si>
     <t>二、工作表說明</t>
